--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3190,6 +3190,116 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126244096</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>604836</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6923306</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sannolikt bohål från tretåig hackspett. Bohålets innerdiameter är ca 4,5 cm och sitter omkring 2m ovan mark i en död gran.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3195,7 +3195,7 @@
         <v>126244096</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,6 +3300,2287 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129339518</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91827</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>658</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>604884</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6923356</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129339099</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91542</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>604943</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6923291</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129338296</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91827</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>658</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>604836</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6923306</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129340708</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>604970</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6923359</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129340170</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>604927</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6923404</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129339952</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91827</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>658</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>604930</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6923439</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129340521</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91827</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>658</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>604965</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6923388</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129339480</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91997</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>604884</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6923356</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129339682</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>604882</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6923394</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129337878</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91827</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>658</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>604921</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6923229</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129339193</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91542</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>604952</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6923317</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129339569</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91542</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>604895</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6923362</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129339832</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91827</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>658</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>604906</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6923435</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129341014</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>604934</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6923350</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129339379</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>604930</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6923339</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129338318</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91997</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>604826</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6923299</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129338152</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91827</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>658</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>604818</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6923289</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129338835</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>604973</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6923267</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129339146</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>604952</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6923317</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129339612</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>604882</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6923385</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129339335</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>604921</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6923330</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129340964</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>604921</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6923330</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129339943</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>604922</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6923448</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129341014</v>
+        <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,38 +4578,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604934</v>
+        <v>604826</v>
       </c>
       <c r="R41" t="n">
-        <v>6923350</v>
+        <v>6923299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4668,7 +4664,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129339379</v>
+        <v>129341014</v>
       </c>
       <c r="B42" t="n">
         <v>98678</v>
@@ -4698,7 +4694,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4707,10 +4703,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604930</v>
+        <v>604934</v>
       </c>
       <c r="R42" t="n">
-        <v>6923339</v>
+        <v>6923350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4769,10 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129338318</v>
+        <v>129339379</v>
       </c>
       <c r="B43" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,34 +4776,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604826</v>
+        <v>604930</v>
       </c>
       <c r="R43" t="n">
-        <v>6923299</v>
+        <v>6923339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,49 +3593,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129340708</v>
+        <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>80050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>604970</v>
+        <v>604927</v>
       </c>
       <c r="R31" t="n">
-        <v>6923359</v>
+        <v>6923404</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,45 +3690,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129340170</v>
+        <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>80050</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>604927</v>
+        <v>604970</v>
       </c>
       <c r="R32" t="n">
-        <v>6923404</v>
+        <v>6923359</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3985,32 +3985,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339480</v>
+        <v>129339193</v>
       </c>
       <c r="B35" t="n">
-        <v>91997</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604884</v>
+        <v>604952</v>
       </c>
       <c r="R35" t="n">
-        <v>6923356</v>
+        <v>6923317</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,32 +4082,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339682</v>
+        <v>129339569</v>
       </c>
       <c r="B36" t="n">
-        <v>80050</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604882</v>
+        <v>604895</v>
       </c>
       <c r="R36" t="n">
-        <v>6923394</v>
+        <v>6923362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
         <v>129337878</v>
       </c>
       <c r="B37" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339193</v>
+        <v>129339832</v>
       </c>
       <c r="B38" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604952</v>
+        <v>604906</v>
       </c>
       <c r="R38" t="n">
-        <v>6923317</v>
+        <v>6923435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339569</v>
+        <v>129339682</v>
       </c>
       <c r="B39" t="n">
-        <v>91542</v>
+        <v>80050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604895</v>
+        <v>604882</v>
       </c>
       <c r="R39" t="n">
-        <v>6923362</v>
+        <v>6923394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339832</v>
+        <v>129339480</v>
       </c>
       <c r="B40" t="n">
-        <v>91827</v>
+        <v>91992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604906</v>
+        <v>604884</v>
       </c>
       <c r="R40" t="n">
-        <v>6923435</v>
+        <v>6923356</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129338318</v>
+        <v>129341014</v>
       </c>
       <c r="B41" t="n">
-        <v>91997</v>
+        <v>98704</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,34 +4578,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604826</v>
+        <v>604934</v>
       </c>
       <c r="R41" t="n">
-        <v>6923299</v>
+        <v>6923350</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4664,10 +4668,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129341014</v>
+        <v>129338318</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>91992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,38 +4679,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604934</v>
+        <v>604826</v>
       </c>
       <c r="R42" t="n">
-        <v>6923350</v>
+        <v>6923299</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,7 +4768,7 @@
         <v>129339379</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>129337878</v>
       </c>
       <c r="B37" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339832</v>
+        <v>129339480</v>
       </c>
       <c r="B38" t="n">
-        <v>91837</v>
+        <v>91993</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604906</v>
+        <v>604884</v>
       </c>
       <c r="R38" t="n">
-        <v>6923435</v>
+        <v>6923356</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339682</v>
+        <v>129339832</v>
       </c>
       <c r="B39" t="n">
-        <v>80050</v>
+        <v>91838</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604882</v>
+        <v>604906</v>
       </c>
       <c r="R39" t="n">
-        <v>6923394</v>
+        <v>6923435</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339480</v>
+        <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>91992</v>
+        <v>80050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604884</v>
+        <v>604882</v>
       </c>
       <c r="R40" t="n">
-        <v>6923356</v>
+        <v>6923394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129341014</v>
+        <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>98704</v>
+        <v>91993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,38 +4578,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604934</v>
+        <v>604826</v>
       </c>
       <c r="R41" t="n">
-        <v>6923350</v>
+        <v>6923299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4668,10 +4664,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129338318</v>
+        <v>129339379</v>
       </c>
       <c r="B42" t="n">
-        <v>91992</v>
+        <v>98705</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4679,34 +4675,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604826</v>
+        <v>604930</v>
       </c>
       <c r="R42" t="n">
-        <v>6923299</v>
+        <v>6923339</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129339379</v>
+        <v>129341014</v>
       </c>
       <c r="B43" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604930</v>
+        <v>604934</v>
       </c>
       <c r="R43" t="n">
-        <v>6923339</v>
+        <v>6923350</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4869,7 +4869,7 @@
         <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3693,7 +3693,7 @@
         <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339193</v>
+        <v>129339569</v>
       </c>
       <c r="B35" t="n">
         <v>91540</v>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604952</v>
+        <v>604895</v>
       </c>
       <c r="R35" t="n">
-        <v>6923317</v>
+        <v>6923362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339569</v>
+        <v>129339193</v>
       </c>
       <c r="B36" t="n">
         <v>91540</v>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604895</v>
+        <v>604952</v>
       </c>
       <c r="R36" t="n">
-        <v>6923362</v>
+        <v>6923317</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129337878</v>
+        <v>129339480</v>
       </c>
       <c r="B37" t="n">
-        <v>91838</v>
+        <v>91993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604921</v>
+        <v>604884</v>
       </c>
       <c r="R37" t="n">
-        <v>6923229</v>
+        <v>6923356</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339480</v>
+        <v>129337878</v>
       </c>
       <c r="B38" t="n">
-        <v>91993</v>
+        <v>91838</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604884</v>
+        <v>604921</v>
       </c>
       <c r="R38" t="n">
-        <v>6923356</v>
+        <v>6923229</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129339379</v>
+        <v>129341014</v>
       </c>
       <c r="B42" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604930</v>
+        <v>604934</v>
       </c>
       <c r="R42" t="n">
-        <v>6923339</v>
+        <v>6923350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129341014</v>
+        <v>129339379</v>
       </c>
       <c r="B43" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604934</v>
+        <v>604930</v>
       </c>
       <c r="R43" t="n">
-        <v>6923350</v>
+        <v>6923339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129338152</v>
+        <v>129338835</v>
       </c>
       <c r="B44" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,34 +4877,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>604818</v>
+        <v>604973</v>
       </c>
       <c r="R44" t="n">
-        <v>6923289</v>
+        <v>6923267</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,6 +4942,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4963,10 +4973,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129338835</v>
+        <v>129338152</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4974,39 +4984,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>604973</v>
+        <v>604818</v>
       </c>
       <c r="R45" t="n">
-        <v>6923267</v>
+        <v>6923289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5039,11 +5044,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>129339569</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>129339193</v>
       </c>
       <c r="B36" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339480</v>
+        <v>129339832</v>
       </c>
       <c r="B37" t="n">
-        <v>91993</v>
+        <v>91841</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604884</v>
+        <v>604906</v>
       </c>
       <c r="R37" t="n">
-        <v>6923356</v>
+        <v>6923435</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
         <v>129337878</v>
       </c>
       <c r="B38" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339832</v>
+        <v>129339480</v>
       </c>
       <c r="B39" t="n">
-        <v>91838</v>
+        <v>91996</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604906</v>
+        <v>604884</v>
       </c>
       <c r="R39" t="n">
-        <v>6923435</v>
+        <v>6923356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4473,7 +4473,7 @@
         <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129338318</v>
+        <v>129339379</v>
       </c>
       <c r="B41" t="n">
-        <v>91993</v>
+        <v>98710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,34 +4578,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604826</v>
+        <v>604930</v>
       </c>
       <c r="R41" t="n">
-        <v>6923299</v>
+        <v>6923339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4667,7 +4671,7 @@
         <v>129341014</v>
       </c>
       <c r="B42" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4765,10 +4769,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129339379</v>
+        <v>129338318</v>
       </c>
       <c r="B43" t="n">
-        <v>98706</v>
+        <v>91996</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4776,38 +4780,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604930</v>
+        <v>604826</v>
       </c>
       <c r="R43" t="n">
-        <v>6923339</v>
+        <v>6923299</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4976,7 +4976,7 @@
         <v>129338152</v>
       </c>
       <c r="B45" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>129339612</v>
       </c>
       <c r="B47" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339480</v>
+        <v>129339682</v>
       </c>
       <c r="B39" t="n">
-        <v>91996</v>
+        <v>80052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604884</v>
+        <v>604882</v>
       </c>
       <c r="R39" t="n">
-        <v>6923356</v>
+        <v>6923394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339682</v>
+        <v>129339480</v>
       </c>
       <c r="B40" t="n">
-        <v>80052</v>
+        <v>91996</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604882</v>
+        <v>604884</v>
       </c>
       <c r="R40" t="n">
-        <v>6923394</v>
+        <v>6923356</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339569</v>
+        <v>129339832</v>
       </c>
       <c r="B35" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604895</v>
+        <v>604906</v>
       </c>
       <c r="R35" t="n">
-        <v>6923362</v>
+        <v>6923435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339193</v>
+        <v>129337878</v>
       </c>
       <c r="B36" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604952</v>
+        <v>604921</v>
       </c>
       <c r="R36" t="n">
-        <v>6923317</v>
+        <v>6923229</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339832</v>
+        <v>129339193</v>
       </c>
       <c r="B37" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604906</v>
+        <v>604952</v>
       </c>
       <c r="R37" t="n">
-        <v>6923435</v>
+        <v>6923317</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129337878</v>
+        <v>129339569</v>
       </c>
       <c r="B38" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604921</v>
+        <v>604895</v>
       </c>
       <c r="R38" t="n">
-        <v>6923229</v>
+        <v>6923362</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339682</v>
+        <v>129339480</v>
       </c>
       <c r="B39" t="n">
-        <v>80052</v>
+        <v>91998</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604882</v>
+        <v>604884</v>
       </c>
       <c r="R39" t="n">
-        <v>6923394</v>
+        <v>6923356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339480</v>
+        <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>91996</v>
+        <v>80053</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604884</v>
+        <v>604882</v>
       </c>
       <c r="R40" t="n">
-        <v>6923356</v>
+        <v>6923394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129339379</v>
+        <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>98710</v>
+        <v>91998</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,38 +4578,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604930</v>
+        <v>604826</v>
       </c>
       <c r="R41" t="n">
-        <v>6923339</v>
+        <v>6923299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4668,10 +4664,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129341014</v>
+        <v>129339379</v>
       </c>
       <c r="B42" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,7 +4694,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4707,10 +4703,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604934</v>
+        <v>604930</v>
       </c>
       <c r="R42" t="n">
-        <v>6923350</v>
+        <v>6923339</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4769,10 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129338318</v>
+        <v>129341014</v>
       </c>
       <c r="B43" t="n">
-        <v>91996</v>
+        <v>98712</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,34 +4776,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604826</v>
+        <v>604934</v>
       </c>
       <c r="R43" t="n">
-        <v>6923299</v>
+        <v>6923350</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129338835</v>
+        <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,39 +4877,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>604973</v>
+        <v>604818</v>
       </c>
       <c r="R44" t="n">
-        <v>6923267</v>
+        <v>6923289</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4942,11 +4937,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4973,10 +4963,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129338152</v>
+        <v>129338835</v>
       </c>
       <c r="B45" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4984,34 +4974,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>604818</v>
+        <v>604973</v>
       </c>
       <c r="R45" t="n">
-        <v>6923289</v>
+        <v>6923267</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,6 +5039,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5180,7 +5180,7 @@
         <v>129339612</v>
       </c>
       <c r="B47" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,45 +3593,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129340170</v>
+        <v>129340708</v>
       </c>
       <c r="B31" t="n">
-        <v>80053</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>604927</v>
+        <v>604970</v>
       </c>
       <c r="R31" t="n">
-        <v>6923404</v>
+        <v>6923359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,49 +3694,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129340708</v>
+        <v>129340170</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>80053</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>604970</v>
+        <v>604927</v>
       </c>
       <c r="R32" t="n">
-        <v>6923359</v>
+        <v>6923404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339832</v>
+        <v>129337878</v>
       </c>
       <c r="B35" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604906</v>
+        <v>604921</v>
       </c>
       <c r="R35" t="n">
-        <v>6923435</v>
+        <v>6923229</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129337878</v>
+        <v>129339569</v>
       </c>
       <c r="B36" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604921</v>
+        <v>604895</v>
       </c>
       <c r="R36" t="n">
-        <v>6923229</v>
+        <v>6923362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
         <v>129339193</v>
       </c>
       <c r="B37" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339569</v>
+        <v>129339832</v>
       </c>
       <c r="B38" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604895</v>
+        <v>604906</v>
       </c>
       <c r="R38" t="n">
-        <v>6923362</v>
+        <v>6923435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4376,7 +4376,7 @@
         <v>129339480</v>
       </c>
       <c r="B39" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>129339379</v>
       </c>
       <c r="B42" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>129341014</v>
       </c>
       <c r="B43" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,49 +3593,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129340708</v>
+        <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>80053</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>604970</v>
+        <v>604927</v>
       </c>
       <c r="R31" t="n">
-        <v>6923359</v>
+        <v>6923404</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,45 +3690,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129340170</v>
+        <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>80053</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>604927</v>
+        <v>604970</v>
       </c>
       <c r="R32" t="n">
-        <v>6923404</v>
+        <v>6923359</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129337878</v>
+        <v>129339832</v>
       </c>
       <c r="B35" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604921</v>
+        <v>604906</v>
       </c>
       <c r="R35" t="n">
-        <v>6923229</v>
+        <v>6923435</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339569</v>
+        <v>129337878</v>
       </c>
       <c r="B36" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604895</v>
+        <v>604921</v>
       </c>
       <c r="R36" t="n">
-        <v>6923362</v>
+        <v>6923229</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339193</v>
+        <v>129339569</v>
       </c>
       <c r="B37" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604952</v>
+        <v>604895</v>
       </c>
       <c r="R37" t="n">
-        <v>6923317</v>
+        <v>6923362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339832</v>
+        <v>129339193</v>
       </c>
       <c r="B38" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604906</v>
+        <v>604952</v>
       </c>
       <c r="R38" t="n">
-        <v>6923435</v>
+        <v>6923317</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4376,7 +4376,7 @@
         <v>129339480</v>
       </c>
       <c r="B39" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>129339379</v>
       </c>
       <c r="B42" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>129341014</v>
       </c>
       <c r="B43" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339832</v>
+        <v>129339193</v>
       </c>
       <c r="B35" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604906</v>
+        <v>604952</v>
       </c>
       <c r="R35" t="n">
-        <v>6923435</v>
+        <v>6923317</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129337878</v>
+        <v>129339569</v>
       </c>
       <c r="B36" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604921</v>
+        <v>604895</v>
       </c>
       <c r="R36" t="n">
-        <v>6923229</v>
+        <v>6923362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339569</v>
+        <v>129339480</v>
       </c>
       <c r="B37" t="n">
-        <v>91550</v>
+        <v>92003</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604895</v>
+        <v>604884</v>
       </c>
       <c r="R37" t="n">
-        <v>6923362</v>
+        <v>6923356</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339193</v>
+        <v>129339682</v>
       </c>
       <c r="B38" t="n">
-        <v>91550</v>
+        <v>80053</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604952</v>
+        <v>604882</v>
       </c>
       <c r="R38" t="n">
-        <v>6923317</v>
+        <v>6923394</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339480</v>
+        <v>129337878</v>
       </c>
       <c r="B39" t="n">
-        <v>92003</v>
+        <v>91848</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604884</v>
+        <v>604921</v>
       </c>
       <c r="R39" t="n">
-        <v>6923356</v>
+        <v>6923229</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339682</v>
+        <v>129339832</v>
       </c>
       <c r="B40" t="n">
-        <v>80053</v>
+        <v>91848</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604882</v>
+        <v>604906</v>
       </c>
       <c r="R40" t="n">
-        <v>6923394</v>
+        <v>6923435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339193</v>
+        <v>129337878</v>
       </c>
       <c r="B35" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604952</v>
+        <v>604921</v>
       </c>
       <c r="R35" t="n">
-        <v>6923317</v>
+        <v>6923229</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339569</v>
+        <v>129339832</v>
       </c>
       <c r="B36" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604895</v>
+        <v>604906</v>
       </c>
       <c r="R36" t="n">
-        <v>6923362</v>
+        <v>6923435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339480</v>
+        <v>129339682</v>
       </c>
       <c r="B37" t="n">
-        <v>92003</v>
+        <v>80053</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604884</v>
+        <v>604882</v>
       </c>
       <c r="R37" t="n">
-        <v>6923356</v>
+        <v>6923394</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339682</v>
+        <v>129339193</v>
       </c>
       <c r="B38" t="n">
-        <v>80053</v>
+        <v>91550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604882</v>
+        <v>604952</v>
       </c>
       <c r="R38" t="n">
-        <v>6923394</v>
+        <v>6923317</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,10 +4373,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129337878</v>
+        <v>129339569</v>
       </c>
       <c r="B39" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4384,21 +4384,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604921</v>
+        <v>604895</v>
       </c>
       <c r="R39" t="n">
-        <v>6923229</v>
+        <v>6923362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339832</v>
+        <v>129339480</v>
       </c>
       <c r="B40" t="n">
-        <v>91848</v>
+        <v>92003</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604906</v>
+        <v>604884</v>
       </c>
       <c r="R40" t="n">
-        <v>6923435</v>
+        <v>6923356</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>129337878</v>
       </c>
       <c r="B35" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4082,32 +4082,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339832</v>
+        <v>129339682</v>
       </c>
       <c r="B36" t="n">
-        <v>91848</v>
+        <v>80053</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R36" t="n">
-        <v>6923435</v>
+        <v>6923394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339682</v>
+        <v>129339569</v>
       </c>
       <c r="B37" t="n">
-        <v>80053</v>
+        <v>91553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604882</v>
+        <v>604895</v>
       </c>
       <c r="R37" t="n">
-        <v>6923394</v>
+        <v>6923362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
         <v>129339193</v>
       </c>
       <c r="B38" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339569</v>
+        <v>129339480</v>
       </c>
       <c r="B39" t="n">
-        <v>91550</v>
+        <v>92006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604895</v>
+        <v>604884</v>
       </c>
       <c r="R39" t="n">
-        <v>6923362</v>
+        <v>6923356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339480</v>
+        <v>129339832</v>
       </c>
       <c r="B40" t="n">
-        <v>92003</v>
+        <v>91851</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604884</v>
+        <v>604906</v>
       </c>
       <c r="R40" t="n">
-        <v>6923356</v>
+        <v>6923435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4570,7 +4570,7 @@
         <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>129339379</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>129341014</v>
       </c>
       <c r="B43" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129338152</v>
+        <v>129338835</v>
       </c>
       <c r="B44" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,34 +4877,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>604818</v>
+        <v>604973</v>
       </c>
       <c r="R44" t="n">
-        <v>6923289</v>
+        <v>6923267</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,6 +4942,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4963,10 +4973,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129338835</v>
+        <v>129338152</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4974,39 +4984,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>604973</v>
+        <v>604818</v>
       </c>
       <c r="R45" t="n">
-        <v>6923267</v>
+        <v>6923289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5039,11 +5044,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129337878</v>
+        <v>129339193</v>
       </c>
       <c r="B35" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604921</v>
+        <v>604952</v>
       </c>
       <c r="R35" t="n">
-        <v>6923229</v>
+        <v>6923317</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,32 +4082,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339682</v>
+        <v>129339569</v>
       </c>
       <c r="B36" t="n">
-        <v>80053</v>
+        <v>91553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604882</v>
+        <v>604895</v>
       </c>
       <c r="R36" t="n">
-        <v>6923394</v>
+        <v>6923362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339569</v>
+        <v>129337878</v>
       </c>
       <c r="B37" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604895</v>
+        <v>604921</v>
       </c>
       <c r="R37" t="n">
-        <v>6923362</v>
+        <v>6923229</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339193</v>
+        <v>129339480</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604952</v>
+        <v>604884</v>
       </c>
       <c r="R38" t="n">
-        <v>6923317</v>
+        <v>6923356</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339480</v>
+        <v>129339832</v>
       </c>
       <c r="B39" t="n">
-        <v>92006</v>
+        <v>91851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604884</v>
+        <v>604906</v>
       </c>
       <c r="R39" t="n">
-        <v>6923356</v>
+        <v>6923435</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339832</v>
+        <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>91851</v>
+        <v>80053</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R40" t="n">
-        <v>6923435</v>
+        <v>6923394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339193</v>
+        <v>129337878</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604952</v>
+        <v>604921</v>
       </c>
       <c r="R35" t="n">
-        <v>6923317</v>
+        <v>6923229</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339569</v>
+        <v>129339832</v>
       </c>
       <c r="B36" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604895</v>
+        <v>604906</v>
       </c>
       <c r="R36" t="n">
-        <v>6923362</v>
+        <v>6923435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129337878</v>
+        <v>129339193</v>
       </c>
       <c r="B37" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604921</v>
+        <v>604952</v>
       </c>
       <c r="R37" t="n">
-        <v>6923229</v>
+        <v>6923317</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339480</v>
+        <v>129339569</v>
       </c>
       <c r="B38" t="n">
-        <v>92006</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604884</v>
+        <v>604895</v>
       </c>
       <c r="R38" t="n">
-        <v>6923356</v>
+        <v>6923362</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339832</v>
+        <v>129339480</v>
       </c>
       <c r="B39" t="n">
-        <v>91851</v>
+        <v>92006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604906</v>
+        <v>604884</v>
       </c>
       <c r="R39" t="n">
-        <v>6923435</v>
+        <v>6923356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129338835</v>
+        <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,39 +4877,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>604973</v>
+        <v>604818</v>
       </c>
       <c r="R44" t="n">
-        <v>6923267</v>
+        <v>6923289</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4942,11 +4937,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4973,10 +4963,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129338152</v>
+        <v>129338835</v>
       </c>
       <c r="B45" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4984,34 +4974,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>604818</v>
+        <v>604973</v>
       </c>
       <c r="R45" t="n">
-        <v>6923289</v>
+        <v>6923267</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,6 +5039,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3985,32 +3985,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129337878</v>
+        <v>129339682</v>
       </c>
       <c r="B35" t="n">
-        <v>91851</v>
+        <v>80053</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604921</v>
+        <v>604882</v>
       </c>
       <c r="R35" t="n">
-        <v>6923229</v>
+        <v>6923394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339832</v>
+        <v>129339193</v>
       </c>
       <c r="B36" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604906</v>
+        <v>604952</v>
       </c>
       <c r="R36" t="n">
-        <v>6923435</v>
+        <v>6923317</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339193</v>
+        <v>129339569</v>
       </c>
       <c r="B37" t="n">
         <v>91553</v>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604952</v>
+        <v>604895</v>
       </c>
       <c r="R37" t="n">
-        <v>6923317</v>
+        <v>6923362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339569</v>
+        <v>129339480</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604895</v>
+        <v>604884</v>
       </c>
       <c r="R38" t="n">
-        <v>6923362</v>
+        <v>6923356</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339480</v>
+        <v>129337878</v>
       </c>
       <c r="B39" t="n">
-        <v>92006</v>
+        <v>91851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604884</v>
+        <v>604921</v>
       </c>
       <c r="R39" t="n">
-        <v>6923356</v>
+        <v>6923229</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339682</v>
+        <v>129339832</v>
       </c>
       <c r="B40" t="n">
-        <v>80053</v>
+        <v>91851</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604882</v>
+        <v>604906</v>
       </c>
       <c r="R40" t="n">
-        <v>6923394</v>
+        <v>6923435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129339379</v>
+        <v>129341014</v>
       </c>
       <c r="B42" t="n">
         <v>98727</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604930</v>
+        <v>604934</v>
       </c>
       <c r="R42" t="n">
-        <v>6923339</v>
+        <v>6923350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129341014</v>
+        <v>129339379</v>
       </c>
       <c r="B43" t="n">
         <v>98727</v>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604934</v>
+        <v>604930</v>
       </c>
       <c r="R43" t="n">
-        <v>6923350</v>
+        <v>6923339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3985,32 +3985,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339682</v>
+        <v>129339193</v>
       </c>
       <c r="B35" t="n">
-        <v>80053</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604882</v>
+        <v>604952</v>
       </c>
       <c r="R35" t="n">
-        <v>6923394</v>
+        <v>6923317</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339193</v>
+        <v>129339569</v>
       </c>
       <c r="B36" t="n">
         <v>91553</v>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604952</v>
+        <v>604895</v>
       </c>
       <c r="R36" t="n">
-        <v>6923317</v>
+        <v>6923362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339569</v>
+        <v>129337878</v>
       </c>
       <c r="B37" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604895</v>
+        <v>604921</v>
       </c>
       <c r="R37" t="n">
-        <v>6923362</v>
+        <v>6923229</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129337878</v>
+        <v>129339832</v>
       </c>
       <c r="B39" t="n">
         <v>91851</v>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604921</v>
+        <v>604906</v>
       </c>
       <c r="R39" t="n">
-        <v>6923229</v>
+        <v>6923435</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339832</v>
+        <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>91851</v>
+        <v>80053</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R40" t="n">
-        <v>6923435</v>
+        <v>6923394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129338318</v>
+        <v>129339379</v>
       </c>
       <c r="B41" t="n">
-        <v>92006</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,34 +4578,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604826</v>
+        <v>604930</v>
       </c>
       <c r="R41" t="n">
-        <v>6923299</v>
+        <v>6923339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4769,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129339379</v>
+        <v>129338318</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>92006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4776,38 +4780,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604930</v>
+        <v>604826</v>
       </c>
       <c r="R43" t="n">
-        <v>6923339</v>
+        <v>6923299</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3593,45 +3593,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129340170</v>
+        <v>129340708</v>
       </c>
       <c r="B31" t="n">
-        <v>80053</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>604927</v>
+        <v>604970</v>
       </c>
       <c r="R31" t="n">
-        <v>6923404</v>
+        <v>6923359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,49 +3694,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129340708</v>
+        <v>129340170</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>80053</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>604970</v>
+        <v>604927</v>
       </c>
       <c r="R32" t="n">
-        <v>6923359</v>
+        <v>6923404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129339379</v>
+        <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>92006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,38 +4578,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604930</v>
+        <v>604826</v>
       </c>
       <c r="R41" t="n">
-        <v>6923339</v>
+        <v>6923299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,10 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129338318</v>
+        <v>129339379</v>
       </c>
       <c r="B43" t="n">
-        <v>92006</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,34 +4776,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604826</v>
+        <v>604930</v>
       </c>
       <c r="R43" t="n">
-        <v>6923299</v>
+        <v>6923339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129338152</v>
+        <v>129338835</v>
       </c>
       <c r="B44" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,34 +4877,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>604818</v>
+        <v>604973</v>
       </c>
       <c r="R44" t="n">
-        <v>6923289</v>
+        <v>6923267</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,6 +4942,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4963,10 +4973,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129338835</v>
+        <v>129338152</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4974,39 +4984,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>604973</v>
+        <v>604818</v>
       </c>
       <c r="R45" t="n">
-        <v>6923267</v>
+        <v>6923289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5039,11 +5044,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3195,7 +3195,7 @@
         <v>126244096</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,49 +3593,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129340708</v>
+        <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>80079</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>604970</v>
+        <v>604927</v>
       </c>
       <c r="R31" t="n">
-        <v>6923359</v>
+        <v>6923404</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,45 +3690,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129340170</v>
+        <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>80053</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>604927</v>
+        <v>604970</v>
       </c>
       <c r="R32" t="n">
-        <v>6923404</v>
+        <v>6923359</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>129339193</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4082,32 +4082,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339569</v>
+        <v>129339480</v>
       </c>
       <c r="B36" t="n">
-        <v>91553</v>
+        <v>92034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604895</v>
+        <v>604884</v>
       </c>
       <c r="R36" t="n">
-        <v>6923362</v>
+        <v>6923356</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
         <v>129337878</v>
       </c>
       <c r="B37" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339480</v>
+        <v>129339832</v>
       </c>
       <c r="B38" t="n">
-        <v>92006</v>
+        <v>91879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604884</v>
+        <v>604906</v>
       </c>
       <c r="R38" t="n">
-        <v>6923356</v>
+        <v>6923435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,10 +4373,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339832</v>
+        <v>129339569</v>
       </c>
       <c r="B39" t="n">
-        <v>91851</v>
+        <v>91581</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4384,21 +4384,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604906</v>
+        <v>604895</v>
       </c>
       <c r="R39" t="n">
-        <v>6923435</v>
+        <v>6923362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4473,7 +4473,7 @@
         <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129338318</v>
+        <v>129339379</v>
       </c>
       <c r="B41" t="n">
-        <v>92006</v>
+        <v>98756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,34 +4578,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604826</v>
+        <v>604930</v>
       </c>
       <c r="R41" t="n">
-        <v>6923299</v>
+        <v>6923339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4667,7 +4671,7 @@
         <v>129341014</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4765,10 +4769,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129339379</v>
+        <v>129338318</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>92034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4776,38 +4780,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604930</v>
+        <v>604826</v>
       </c>
       <c r="R43" t="n">
-        <v>6923339</v>
+        <v>6923299</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129338835</v>
+        <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,39 +4877,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>604973</v>
+        <v>604818</v>
       </c>
       <c r="R44" t="n">
-        <v>6923267</v>
+        <v>6923289</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4942,11 +4937,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4973,10 +4963,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129338152</v>
+        <v>129338835</v>
       </c>
       <c r="B45" t="n">
-        <v>91851</v>
+        <v>57730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4984,34 +4974,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>604818</v>
+        <v>604973</v>
       </c>
       <c r="R45" t="n">
-        <v>6923289</v>
+        <v>6923267</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,6 +5039,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5073,7 +5073,7 @@
         <v>129339146</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>129339612</v>
       </c>
       <c r="B47" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>129340964</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3195,7 +3195,7 @@
         <v>126244096</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339193</v>
+        <v>129337878</v>
       </c>
       <c r="B35" t="n">
-        <v>91581</v>
+        <v>91885</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604952</v>
+        <v>604921</v>
       </c>
       <c r="R35" t="n">
-        <v>6923317</v>
+        <v>6923229</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,32 +4082,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339480</v>
+        <v>129339832</v>
       </c>
       <c r="B36" t="n">
-        <v>92034</v>
+        <v>91885</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604884</v>
+        <v>604906</v>
       </c>
       <c r="R36" t="n">
-        <v>6923356</v>
+        <v>6923435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129337878</v>
+        <v>129339193</v>
       </c>
       <c r="B37" t="n">
-        <v>91879</v>
+        <v>91587</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604921</v>
+        <v>604952</v>
       </c>
       <c r="R37" t="n">
-        <v>6923229</v>
+        <v>6923317</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339832</v>
+        <v>129339569</v>
       </c>
       <c r="B38" t="n">
-        <v>91879</v>
+        <v>91587</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604906</v>
+        <v>604895</v>
       </c>
       <c r="R38" t="n">
-        <v>6923435</v>
+        <v>6923362</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339569</v>
+        <v>129339480</v>
       </c>
       <c r="B39" t="n">
-        <v>91581</v>
+        <v>92040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604895</v>
+        <v>604884</v>
       </c>
       <c r="R39" t="n">
-        <v>6923362</v>
+        <v>6923356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4473,7 +4473,7 @@
         <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129339379</v>
+        <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>92040</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,38 +4578,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604930</v>
+        <v>604826</v>
       </c>
       <c r="R41" t="n">
-        <v>6923339</v>
+        <v>6923299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4671,7 +4667,7 @@
         <v>129341014</v>
       </c>
       <c r="B42" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4769,10 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129338318</v>
+        <v>129339379</v>
       </c>
       <c r="B43" t="n">
-        <v>92034</v>
+        <v>98768</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,34 +4776,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604826</v>
+        <v>604930</v>
       </c>
       <c r="R43" t="n">
-        <v>6923299</v>
+        <v>6923339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4869,7 +4869,7 @@
         <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>129338835</v>
       </c>
       <c r="B45" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>129339146</v>
       </c>
       <c r="B46" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>129339612</v>
       </c>
       <c r="B47" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129339335</v>
       </c>
       <c r="B48" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>129340964</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>129339943</v>
       </c>
       <c r="B50" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126244910</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126244779</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>126242691</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>126244721</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>126242541</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126242290</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>126244096</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129337878</v>
+        <v>129339193</v>
       </c>
       <c r="B35" t="n">
-        <v>91885</v>
+        <v>91588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604921</v>
+        <v>604952</v>
       </c>
       <c r="R35" t="n">
-        <v>6923229</v>
+        <v>6923317</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339832</v>
+        <v>129339569</v>
       </c>
       <c r="B36" t="n">
-        <v>91885</v>
+        <v>91588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604906</v>
+        <v>604895</v>
       </c>
       <c r="R36" t="n">
-        <v>6923435</v>
+        <v>6923362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339193</v>
+        <v>129337878</v>
       </c>
       <c r="B37" t="n">
-        <v>91587</v>
+        <v>91886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604952</v>
+        <v>604921</v>
       </c>
       <c r="R37" t="n">
-        <v>6923317</v>
+        <v>6923229</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339569</v>
+        <v>129339480</v>
       </c>
       <c r="B38" t="n">
-        <v>91587</v>
+        <v>92041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604895</v>
+        <v>604884</v>
       </c>
       <c r="R38" t="n">
-        <v>6923362</v>
+        <v>6923356</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339480</v>
+        <v>129339832</v>
       </c>
       <c r="B39" t="n">
-        <v>92040</v>
+        <v>91886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604884</v>
+        <v>604906</v>
       </c>
       <c r="R39" t="n">
-        <v>6923356</v>
+        <v>6923435</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4473,7 +4473,7 @@
         <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129341014</v>
+        <v>129339379</v>
       </c>
       <c r="B42" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604934</v>
+        <v>604930</v>
       </c>
       <c r="R42" t="n">
-        <v>6923350</v>
+        <v>6923339</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129339379</v>
+        <v>129341014</v>
       </c>
       <c r="B43" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604930</v>
+        <v>604934</v>
       </c>
       <c r="R43" t="n">
-        <v>6923339</v>
+        <v>6923350</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4869,7 +4869,7 @@
         <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4963,50 +4963,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129338835</v>
+        <v>129339612</v>
       </c>
       <c r="B45" t="n">
-        <v>57735</v>
+        <v>80085</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>604973</v>
+        <v>604882</v>
       </c>
       <c r="R45" t="n">
-        <v>6923267</v>
+        <v>6923385</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5039,11 +5034,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5070,38 +5060,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129339146</v>
+        <v>129339335</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>38</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5110,10 +5099,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>604952</v>
+        <v>604921</v>
       </c>
       <c r="R46" t="n">
-        <v>6923317</v>
+        <v>6923330</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5146,11 +5135,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5177,45 +5161,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129339612</v>
+        <v>129339943</v>
       </c>
       <c r="B47" t="n">
-        <v>80084</v>
+        <v>98769</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>604882</v>
+        <v>604922</v>
       </c>
       <c r="R47" t="n">
-        <v>6923385</v>
+        <v>6923448</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5274,37 +5262,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129339335</v>
+        <v>129338835</v>
       </c>
       <c r="B48" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>38</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5313,10 +5302,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>604921</v>
+        <v>604973</v>
       </c>
       <c r="R48" t="n">
-        <v>6923330</v>
+        <v>6923267</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,6 +5338,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5375,10 +5369,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129340964</v>
+        <v>129339146</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5415,10 +5409,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>604921</v>
+        <v>604952</v>
       </c>
       <c r="R49" t="n">
-        <v>6923330</v>
+        <v>6923317</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5482,37 +5476,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129339943</v>
+        <v>129340964</v>
       </c>
       <c r="B50" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5521,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>604922</v>
+        <v>604921</v>
       </c>
       <c r="R50" t="n">
-        <v>6923448</v>
+        <v>6923330</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5557,6 +5552,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3305,7 +3305,7 @@
         <v>129339518</v>
       </c>
       <c r="B28" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129339099</v>
       </c>
       <c r="B29" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129338296</v>
       </c>
       <c r="B30" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129339952</v>
       </c>
       <c r="B33" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129340521</v>
       </c>
       <c r="B34" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>129339193</v>
       </c>
       <c r="B35" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>129339569</v>
       </c>
       <c r="B36" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129337878</v>
+        <v>129339480</v>
       </c>
       <c r="B37" t="n">
-        <v>91886</v>
+        <v>92046</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604921</v>
+        <v>604884</v>
       </c>
       <c r="R37" t="n">
-        <v>6923229</v>
+        <v>6923356</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339480</v>
+        <v>129339832</v>
       </c>
       <c r="B38" t="n">
-        <v>92041</v>
+        <v>91891</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604884</v>
+        <v>604906</v>
       </c>
       <c r="R38" t="n">
-        <v>6923356</v>
+        <v>6923435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339832</v>
+        <v>129339682</v>
       </c>
       <c r="B39" t="n">
-        <v>91886</v>
+        <v>80090</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R39" t="n">
-        <v>6923435</v>
+        <v>6923394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339682</v>
+        <v>129337878</v>
       </c>
       <c r="B40" t="n">
-        <v>80085</v>
+        <v>91891</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604882</v>
+        <v>604921</v>
       </c>
       <c r="R40" t="n">
-        <v>6923394</v>
+        <v>6923229</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129338318</v>
+        <v>129341014</v>
       </c>
       <c r="B41" t="n">
-        <v>92041</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,34 +4578,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604826</v>
+        <v>604934</v>
       </c>
       <c r="R41" t="n">
-        <v>6923299</v>
+        <v>6923350</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4667,7 +4671,7 @@
         <v>129339379</v>
       </c>
       <c r="B42" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4765,10 +4769,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129341014</v>
+        <v>129338318</v>
       </c>
       <c r="B43" t="n">
-        <v>98769</v>
+        <v>92046</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4776,38 +4780,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604934</v>
+        <v>604826</v>
       </c>
       <c r="R43" t="n">
-        <v>6923350</v>
+        <v>6923299</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4869,7 +4869,7 @@
         <v>129338152</v>
       </c>
       <c r="B44" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>129339612</v>
       </c>
       <c r="B45" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>129339335</v>
       </c>
       <c r="B46" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>129339943</v>
       </c>
       <c r="B47" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3593,45 +3593,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129340170</v>
+        <v>129340708</v>
       </c>
       <c r="B31" t="n">
-        <v>80090</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>604927</v>
+        <v>604970</v>
       </c>
       <c r="R31" t="n">
-        <v>6923404</v>
+        <v>6923359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,49 +3694,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129340708</v>
+        <v>129340170</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>80090</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>604970</v>
+        <v>604927</v>
       </c>
       <c r="R32" t="n">
-        <v>6923359</v>
+        <v>6923404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,32 +3985,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339193</v>
+        <v>129339480</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604952</v>
+        <v>604884</v>
       </c>
       <c r="R35" t="n">
-        <v>6923317</v>
+        <v>6923356</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,32 +4082,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339569</v>
+        <v>129339682</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>80090</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604895</v>
+        <v>604882</v>
       </c>
       <c r="R36" t="n">
-        <v>6923362</v>
+        <v>6923394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339480</v>
+        <v>129339193</v>
       </c>
       <c r="B37" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604884</v>
+        <v>604952</v>
       </c>
       <c r="R37" t="n">
-        <v>6923356</v>
+        <v>6923317</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339832</v>
+        <v>129339569</v>
       </c>
       <c r="B38" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604906</v>
+        <v>604895</v>
       </c>
       <c r="R38" t="n">
-        <v>6923435</v>
+        <v>6923362</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4373,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339682</v>
+        <v>129337878</v>
       </c>
       <c r="B39" t="n">
-        <v>80090</v>
+        <v>91891</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604882</v>
+        <v>604921</v>
       </c>
       <c r="R39" t="n">
-        <v>6923394</v>
+        <v>6923229</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129337878</v>
+        <v>129339832</v>
       </c>
       <c r="B40" t="n">
         <v>91891</v>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604921</v>
+        <v>604906</v>
       </c>
       <c r="R40" t="n">
-        <v>6923229</v>
+        <v>6923435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129341014</v>
+        <v>129339379</v>
       </c>
       <c r="B41" t="n">
         <v>98774</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604934</v>
+        <v>604930</v>
       </c>
       <c r="R41" t="n">
-        <v>6923350</v>
+        <v>6923339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129339379</v>
+        <v>129341014</v>
       </c>
       <c r="B42" t="n">
         <v>98774</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604930</v>
+        <v>604934</v>
       </c>
       <c r="R42" t="n">
-        <v>6923339</v>
+        <v>6923350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -3593,49 +3593,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129340708</v>
+        <v>129340170</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>80090</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>604970</v>
+        <v>604927</v>
       </c>
       <c r="R31" t="n">
-        <v>6923359</v>
+        <v>6923404</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,45 +3690,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129340170</v>
+        <v>129340708</v>
       </c>
       <c r="B32" t="n">
-        <v>80090</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>604927</v>
+        <v>604970</v>
       </c>
       <c r="R32" t="n">
-        <v>6923404</v>
+        <v>6923359</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,32 +3985,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339480</v>
+        <v>129339193</v>
       </c>
       <c r="B35" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604884</v>
+        <v>604952</v>
       </c>
       <c r="R35" t="n">
-        <v>6923356</v>
+        <v>6923317</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4082,32 +4082,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339682</v>
+        <v>129339569</v>
       </c>
       <c r="B36" t="n">
-        <v>80090</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604882</v>
+        <v>604895</v>
       </c>
       <c r="R36" t="n">
-        <v>6923394</v>
+        <v>6923362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129339193</v>
+        <v>129337878</v>
       </c>
       <c r="B37" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604952</v>
+        <v>604921</v>
       </c>
       <c r="R37" t="n">
-        <v>6923317</v>
+        <v>6923229</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4276,32 +4276,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339569</v>
+        <v>129339480</v>
       </c>
       <c r="B38" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604895</v>
+        <v>604884</v>
       </c>
       <c r="R38" t="n">
-        <v>6923362</v>
+        <v>6923356</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129337878</v>
+        <v>129339832</v>
       </c>
       <c r="B39" t="n">
         <v>91891</v>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604921</v>
+        <v>604906</v>
       </c>
       <c r="R39" t="n">
-        <v>6923229</v>
+        <v>6923435</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339832</v>
+        <v>129339682</v>
       </c>
       <c r="B40" t="n">
-        <v>91891</v>
+        <v>80090</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R40" t="n">
-        <v>6923435</v>
+        <v>6923394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129339379</v>
+        <v>129338318</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>92046</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,38 +4578,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604930</v>
+        <v>604826</v>
       </c>
       <c r="R41" t="n">
-        <v>6923339</v>
+        <v>6923299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,10 +4765,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129338318</v>
+        <v>129339379</v>
       </c>
       <c r="B43" t="n">
-        <v>92046</v>
+        <v>98774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,34 +4776,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604826</v>
+        <v>604930</v>
       </c>
       <c r="R43" t="n">
-        <v>6923299</v>
+        <v>6923339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126244910</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126244779</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>126242691</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>126244721</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>126242541</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126242290</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>126244096</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>129338835</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>129339146</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>129340964</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5581,6 +5581,1973 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132622591</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>604963</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6923375</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132622592</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>604966</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6923358</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132622587</v>
+      </c>
+      <c r="B53" t="n">
+        <v>75423</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>604903</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6923396</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132622594</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79349</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>185</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>604901</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6923297</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132623165</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57127</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>604935</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6923321</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132622593</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57127</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>604969</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6923321</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132622600</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79349</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>185</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>604927</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6923203</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132622589</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>604906</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6923397</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>130 ex</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132622598</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>604882</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6923306</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132622586</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79573</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>604933</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6923265</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132622597</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>604883</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6923304</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132622590</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>604925</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6923398</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132622599</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79349</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>185</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>604882</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6923308</v>
+      </c>
+      <c r="S63" t="n">
+        <v>6</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132622601</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79349</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>185</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>604915</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6923304</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132622596</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79349</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>185</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>604888</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6923300</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132623161</v>
+      </c>
+      <c r="B66" t="n">
+        <v>58109</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>604889</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6923338</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132622595</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79349</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>185</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>604886</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6923295</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132623034</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>604910</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6923344</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Sannolikt ett par som trummar i duett.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5586,7 +5586,7 @@
         <v>132622591</v>
       </c>
       <c r="B51" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>132622592</v>
       </c>
       <c r="B52" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>132622587</v>
       </c>
       <c r="B53" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>132622594</v>
       </c>
       <c r="B54" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132623165</v>
+        <v>132622600</v>
       </c>
       <c r="B55" t="n">
-        <v>57127</v>
+        <v>79351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,49 +6022,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>604935</v>
+        <v>604927</v>
       </c>
       <c r="R55" t="n">
-        <v>6923321</v>
+        <v>6923203</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6091,9 +6079,19 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6120,10 +6118,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132622593</v>
+        <v>132623165</v>
       </c>
       <c r="B56" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6163,17 +6161,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>604969</v>
+        <v>604935</v>
       </c>
       <c r="R56" t="n">
         <v>6923321</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6197,22 +6195,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6239,10 +6227,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132622600</v>
+        <v>132622593</v>
       </c>
       <c r="B57" t="n">
-        <v>79349</v>
+        <v>57128</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6250,34 +6238,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>604927</v>
+        <v>604969</v>
       </c>
       <c r="R57" t="n">
-        <v>6923203</v>
+        <v>6923321</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6304,22 +6304,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6349,7 +6349,7 @@
         <v>132622589</v>
       </c>
       <c r="B58" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>132622598</v>
       </c>
       <c r="B59" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>132622586</v>
       </c>
       <c r="B60" t="n">
-        <v>79573</v>
+        <v>79575</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>132622597</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622599</v>
+        <v>132622601</v>
       </c>
       <c r="B63" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604882</v>
+        <v>604915</v>
       </c>
       <c r="R63" t="n">
-        <v>6923308</v>
+        <v>6923304</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,10 +7006,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622601</v>
+        <v>132622599</v>
       </c>
       <c r="B64" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604915</v>
+        <v>604882</v>
       </c>
       <c r="R64" t="n">
-        <v>6923304</v>
+        <v>6923308</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7071,22 +7071,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7113,10 +7113,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132622596</v>
+        <v>132623161</v>
       </c>
       <c r="B65" t="n">
-        <v>79349</v>
+        <v>58110</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7124,37 +7124,49 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>604888</v>
+        <v>604889</v>
       </c>
       <c r="R65" t="n">
-        <v>6923300</v>
+        <v>6923338</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7178,22 +7190,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7220,10 +7222,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132623161</v>
+        <v>132622596</v>
       </c>
       <c r="B66" t="n">
-        <v>58109</v>
+        <v>79351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7231,49 +7233,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>604889</v>
+        <v>604888</v>
       </c>
       <c r="R66" t="n">
-        <v>6923338</v>
+        <v>6923300</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7297,12 +7287,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132622595</v>
+        <v>132623034</v>
       </c>
       <c r="B67" t="n">
-        <v>79349</v>
+        <v>57949</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7340,37 +7340,49 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>604886</v>
+        <v>604910</v>
       </c>
       <c r="R67" t="n">
-        <v>6923295</v>
+        <v>6923344</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7394,22 +7406,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Sannolikt ett par som trummar i duett.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7436,10 +7443,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132623034</v>
+        <v>132622595</v>
       </c>
       <c r="B68" t="n">
-        <v>57948</v>
+        <v>79351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7447,49 +7454,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>604910</v>
+        <v>604886</v>
       </c>
       <c r="R68" t="n">
-        <v>6923344</v>
+        <v>6923295</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7513,17 +7508,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Sannolikt ett par som trummar i duett.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -6011,10 +6011,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132622600</v>
+        <v>132623165</v>
       </c>
       <c r="B55" t="n">
-        <v>79351</v>
+        <v>57128</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,37 +6022,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>604927</v>
+        <v>604935</v>
       </c>
       <c r="R55" t="n">
-        <v>6923203</v>
+        <v>6923321</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6079,19 +6091,9 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>17:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6118,7 +6120,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132623165</v>
+        <v>132622593</v>
       </c>
       <c r="B56" t="n">
         <v>57128</v>
@@ -6161,17 +6163,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>604935</v>
+        <v>604969</v>
       </c>
       <c r="R56" t="n">
         <v>6923321</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6195,12 +6197,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,10 +6239,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132622593</v>
+        <v>132622600</v>
       </c>
       <c r="B57" t="n">
-        <v>57128</v>
+        <v>79351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6238,46 +6250,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>604969</v>
+        <v>604927</v>
       </c>
       <c r="R57" t="n">
-        <v>6923321</v>
+        <v>6923203</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6304,22 +6304,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6346,32 +6346,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132622589</v>
+        <v>132622598</v>
       </c>
       <c r="B58" t="n">
-        <v>99106</v>
+        <v>79319</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R58" t="n">
-        <v>6923397</v>
+        <v>6923306</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6426,12 +6426,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>130 ex</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6458,32 +6453,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132622598</v>
+        <v>132622589</v>
       </c>
       <c r="B59" t="n">
-        <v>79319</v>
+        <v>99106</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6493,10 +6488,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>604882</v>
+        <v>604906</v>
       </c>
       <c r="R59" t="n">
-        <v>6923306</v>
+        <v>6923397</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6528,7 +6523,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6538,7 +6533,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>130 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622591</v>
+        <v>132622592</v>
       </c>
       <c r="B51" t="n">
-        <v>79319</v>
+        <v>91908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604963</v>
+        <v>604966</v>
       </c>
       <c r="R51" t="n">
-        <v>6923375</v>
+        <v>6923358</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622592</v>
+        <v>132622591</v>
       </c>
       <c r="B52" t="n">
-        <v>91898</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604966</v>
+        <v>604963</v>
       </c>
       <c r="R52" t="n">
-        <v>6923358</v>
+        <v>6923375</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5800,7 +5800,7 @@
         <v>132622587</v>
       </c>
       <c r="B53" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>132622594</v>
       </c>
       <c r="B54" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132623165</v>
+        <v>132622600</v>
       </c>
       <c r="B55" t="n">
-        <v>57128</v>
+        <v>79359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,49 +6022,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>604935</v>
+        <v>604927</v>
       </c>
       <c r="R55" t="n">
-        <v>6923321</v>
+        <v>6923203</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6091,9 +6079,19 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6120,10 +6118,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132622593</v>
+        <v>132623165</v>
       </c>
       <c r="B56" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6163,17 +6161,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>604969</v>
+        <v>604935</v>
       </c>
       <c r="R56" t="n">
         <v>6923321</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6197,22 +6195,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6239,10 +6227,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132622600</v>
+        <v>132622593</v>
       </c>
       <c r="B57" t="n">
-        <v>79351</v>
+        <v>57132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6250,34 +6238,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>604927</v>
+        <v>604969</v>
       </c>
       <c r="R57" t="n">
-        <v>6923203</v>
+        <v>6923321</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6304,22 +6304,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6346,32 +6346,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132622598</v>
+        <v>132622589</v>
       </c>
       <c r="B58" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>604882</v>
+        <v>604906</v>
       </c>
       <c r="R58" t="n">
-        <v>6923306</v>
+        <v>6923397</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6426,7 +6426,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>130 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6453,32 +6458,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132622589</v>
+        <v>132622598</v>
       </c>
       <c r="B59" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6488,10 +6493,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R59" t="n">
-        <v>6923397</v>
+        <v>6923306</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6523,7 +6528,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6533,12 +6538,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>130 ex</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6568,7 +6568,7 @@
         <v>132622586</v>
       </c>
       <c r="B60" t="n">
-        <v>79575</v>
+        <v>79583</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>132622597</v>
       </c>
       <c r="B61" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6792,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132622590</v>
+        <v>132622601</v>
       </c>
       <c r="B62" t="n">
-        <v>5199</v>
+        <v>79359</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>604925</v>
+        <v>604915</v>
       </c>
       <c r="R62" t="n">
-        <v>6923398</v>
+        <v>6923304</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6899,10 +6899,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622601</v>
+        <v>132622599</v>
       </c>
       <c r="B63" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604915</v>
+        <v>604882</v>
       </c>
       <c r="R63" t="n">
-        <v>6923304</v>
+        <v>6923308</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,32 +7006,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622599</v>
+        <v>132622590</v>
       </c>
       <c r="B64" t="n">
-        <v>79351</v>
+        <v>5199</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604882</v>
+        <v>604925</v>
       </c>
       <c r="R64" t="n">
-        <v>6923308</v>
+        <v>6923398</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7113,10 +7113,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132623161</v>
+        <v>132622596</v>
       </c>
       <c r="B65" t="n">
-        <v>58110</v>
+        <v>79359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7124,49 +7124,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>604889</v>
+        <v>604888</v>
       </c>
       <c r="R65" t="n">
-        <v>6923338</v>
+        <v>6923300</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7190,12 +7178,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7222,10 +7220,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132622596</v>
+        <v>132623161</v>
       </c>
       <c r="B66" t="n">
-        <v>79351</v>
+        <v>58114</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7233,37 +7231,49 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>604888</v>
+        <v>604889</v>
       </c>
       <c r="R66" t="n">
-        <v>6923300</v>
+        <v>6923338</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7287,22 +7297,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7332,7 +7332,7 @@
         <v>132623034</v>
       </c>
       <c r="B67" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>132622595</v>
       </c>
       <c r="B68" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622592</v>
+        <v>132622591</v>
       </c>
       <c r="B51" t="n">
-        <v>91908</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604966</v>
+        <v>604963</v>
       </c>
       <c r="R51" t="n">
-        <v>6923358</v>
+        <v>6923375</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622591</v>
+        <v>132622592</v>
       </c>
       <c r="B52" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604963</v>
+        <v>604966</v>
       </c>
       <c r="R52" t="n">
-        <v>6923375</v>
+        <v>6923358</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6346,32 +6346,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132622589</v>
+        <v>132622598</v>
       </c>
       <c r="B58" t="n">
-        <v>99116</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R58" t="n">
-        <v>6923397</v>
+        <v>6923306</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6426,12 +6426,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>130 ex</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6458,32 +6453,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132622598</v>
+        <v>132622589</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>99117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6493,10 +6488,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>604882</v>
+        <v>604906</v>
       </c>
       <c r="R59" t="n">
-        <v>6923306</v>
+        <v>6923397</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6528,7 +6523,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6538,7 +6533,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>130 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132623034</v>
+        <v>132622595</v>
       </c>
       <c r="B67" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7340,49 +7340,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>604910</v>
+        <v>604886</v>
       </c>
       <c r="R67" t="n">
-        <v>6923344</v>
+        <v>6923295</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7406,17 +7394,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Sannolikt ett par som trummar i duett.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7443,10 +7436,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132622595</v>
+        <v>132623034</v>
       </c>
       <c r="B68" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7454,37 +7447,49 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>604886</v>
+        <v>604910</v>
       </c>
       <c r="R68" t="n">
-        <v>6923295</v>
+        <v>6923344</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7508,22 +7513,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Sannolikt ett par som trummar i duett.</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622591</v>
+        <v>132622592</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604963</v>
+        <v>604966</v>
       </c>
       <c r="R51" t="n">
-        <v>6923375</v>
+        <v>6923358</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622592</v>
+        <v>132622591</v>
       </c>
       <c r="B52" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604966</v>
+        <v>604963</v>
       </c>
       <c r="R52" t="n">
-        <v>6923358</v>
+        <v>6923375</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6456,7 +6456,7 @@
         <v>132622589</v>
       </c>
       <c r="B59" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132622595</v>
+        <v>132623034</v>
       </c>
       <c r="B67" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7340,37 +7340,49 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>604886</v>
+        <v>604910</v>
       </c>
       <c r="R67" t="n">
-        <v>6923295</v>
+        <v>6923344</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7394,22 +7406,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Sannolikt ett par som trummar i duett.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7436,10 +7443,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132623034</v>
+        <v>132622595</v>
       </c>
       <c r="B68" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7447,49 +7454,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>604910</v>
+        <v>604886</v>
       </c>
       <c r="R68" t="n">
-        <v>6923344</v>
+        <v>6923295</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7513,17 +7508,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Sannolikt ett par som trummar i duett.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -7329,10 +7329,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132623034</v>
+        <v>132622595</v>
       </c>
       <c r="B67" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7340,49 +7340,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>604910</v>
+        <v>604886</v>
       </c>
       <c r="R67" t="n">
-        <v>6923344</v>
+        <v>6923295</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7406,17 +7394,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Sannolikt ett par som trummar i duett.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7443,10 +7436,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132622595</v>
+        <v>132623034</v>
       </c>
       <c r="B68" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7454,37 +7447,49 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>604886</v>
+        <v>604910</v>
       </c>
       <c r="R68" t="n">
-        <v>6923295</v>
+        <v>6923344</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7508,22 +7513,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Sannolikt ett par som trummar i duett.</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622592</v>
+        <v>132622591</v>
       </c>
       <c r="B51" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604966</v>
+        <v>604963</v>
       </c>
       <c r="R51" t="n">
-        <v>6923358</v>
+        <v>6923375</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622591</v>
+        <v>132622592</v>
       </c>
       <c r="B52" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604963</v>
+        <v>604966</v>
       </c>
       <c r="R52" t="n">
-        <v>6923375</v>
+        <v>6923358</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6346,32 +6346,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132622598</v>
+        <v>132622589</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>604882</v>
+        <v>604906</v>
       </c>
       <c r="R58" t="n">
-        <v>6923306</v>
+        <v>6923397</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6426,7 +6426,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>130 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6453,32 +6458,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132622589</v>
+        <v>132622598</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6488,10 +6493,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R59" t="n">
-        <v>6923397</v>
+        <v>6923306</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6523,7 +6528,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6533,12 +6538,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>130 ex</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6792,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132622601</v>
+        <v>132622590</v>
       </c>
       <c r="B62" t="n">
-        <v>79359</v>
+        <v>5199</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>604915</v>
+        <v>604925</v>
       </c>
       <c r="R62" t="n">
-        <v>6923304</v>
+        <v>6923398</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6899,7 +6899,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622599</v>
+        <v>132622601</v>
       </c>
       <c r="B63" t="n">
         <v>79359</v>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604882</v>
+        <v>604915</v>
       </c>
       <c r="R63" t="n">
-        <v>6923308</v>
+        <v>6923304</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,32 +7006,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622590</v>
+        <v>132622599</v>
       </c>
       <c r="B64" t="n">
-        <v>5199</v>
+        <v>79359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604925</v>
+        <v>604882</v>
       </c>
       <c r="R64" t="n">
-        <v>6923398</v>
+        <v>6923308</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7113,10 +7113,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132622596</v>
+        <v>132623161</v>
       </c>
       <c r="B65" t="n">
-        <v>79359</v>
+        <v>58114</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7124,37 +7124,49 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>604888</v>
+        <v>604889</v>
       </c>
       <c r="R65" t="n">
-        <v>6923300</v>
+        <v>6923338</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7178,22 +7190,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7220,10 +7222,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132623161</v>
+        <v>132622596</v>
       </c>
       <c r="B66" t="n">
-        <v>58114</v>
+        <v>79359</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7231,49 +7233,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>604889</v>
+        <v>604888</v>
       </c>
       <c r="R66" t="n">
-        <v>6923338</v>
+        <v>6923300</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7297,12 +7287,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132622595</v>
+        <v>132623034</v>
       </c>
       <c r="B67" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7340,37 +7340,49 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>604886</v>
+        <v>604910</v>
       </c>
       <c r="R67" t="n">
-        <v>6923295</v>
+        <v>6923344</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7394,22 +7406,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Sannolikt ett par som trummar i duett.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7436,10 +7443,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132623034</v>
+        <v>132622595</v>
       </c>
       <c r="B68" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7447,49 +7454,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>604910</v>
+        <v>604886</v>
       </c>
       <c r="R68" t="n">
-        <v>6923344</v>
+        <v>6923295</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7513,17 +7508,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Sannolikt ett par som trummar i duett.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -6792,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132622590</v>
+        <v>132622601</v>
       </c>
       <c r="B62" t="n">
-        <v>5199</v>
+        <v>79359</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>604925</v>
+        <v>604915</v>
       </c>
       <c r="R62" t="n">
-        <v>6923398</v>
+        <v>6923304</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6899,7 +6899,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622601</v>
+        <v>132622599</v>
       </c>
       <c r="B63" t="n">
         <v>79359</v>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604915</v>
+        <v>604882</v>
       </c>
       <c r="R63" t="n">
-        <v>6923304</v>
+        <v>6923308</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,32 +7006,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622599</v>
+        <v>132622590</v>
       </c>
       <c r="B64" t="n">
-        <v>79359</v>
+        <v>5199</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604882</v>
+        <v>604925</v>
       </c>
       <c r="R64" t="n">
-        <v>6923308</v>
+        <v>6923398</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7329,10 +7329,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132623034</v>
+        <v>132622595</v>
       </c>
       <c r="B67" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7340,49 +7340,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>604910</v>
+        <v>604886</v>
       </c>
       <c r="R67" t="n">
-        <v>6923344</v>
+        <v>6923295</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7406,17 +7394,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Sannolikt ett par som trummar i duett.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7443,10 +7436,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132622595</v>
+        <v>132623034</v>
       </c>
       <c r="B68" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7454,37 +7447,49 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>604886</v>
+        <v>604910</v>
       </c>
       <c r="R68" t="n">
-        <v>6923295</v>
+        <v>6923344</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7508,22 +7513,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Sannolikt ett par som trummar i duett.</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622591</v>
+        <v>132622592</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>91910</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604963</v>
+        <v>604966</v>
       </c>
       <c r="R51" t="n">
-        <v>6923375</v>
+        <v>6923358</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622592</v>
+        <v>132622591</v>
       </c>
       <c r="B52" t="n">
-        <v>91909</v>
+        <v>79328</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604966</v>
+        <v>604963</v>
       </c>
       <c r="R52" t="n">
-        <v>6923358</v>
+        <v>6923375</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5800,7 +5800,7 @@
         <v>132622587</v>
       </c>
       <c r="B53" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>132622594</v>
       </c>
       <c r="B54" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>132622600</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>132623165</v>
       </c>
       <c r="B56" t="n">
-        <v>57132</v>
+        <v>57133</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>132622593</v>
       </c>
       <c r="B57" t="n">
-        <v>57132</v>
+        <v>57133</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>132622589</v>
       </c>
       <c r="B58" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>132622598</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>132622586</v>
       </c>
       <c r="B60" t="n">
-        <v>79583</v>
+        <v>79584</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>132622597</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>132622601</v>
       </c>
       <c r="B62" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>132622599</v>
       </c>
       <c r="B63" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132623161</v>
+        <v>132622596</v>
       </c>
       <c r="B65" t="n">
-        <v>58114</v>
+        <v>79360</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7124,49 +7124,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>604889</v>
+        <v>604888</v>
       </c>
       <c r="R65" t="n">
-        <v>6923338</v>
+        <v>6923300</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7190,12 +7178,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7222,10 +7220,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132622596</v>
+        <v>132623161</v>
       </c>
       <c r="B66" t="n">
-        <v>79359</v>
+        <v>58115</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7233,37 +7231,49 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>604888</v>
+        <v>604889</v>
       </c>
       <c r="R66" t="n">
-        <v>6923300</v>
+        <v>6923338</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7287,22 +7297,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7332,7 +7332,7 @@
         <v>132622595</v>
       </c>
       <c r="B67" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>132623034</v>
       </c>
       <c r="B68" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622591</v>
+        <v>132622592</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604963</v>
+        <v>604966</v>
       </c>
       <c r="R51" t="n">
-        <v>6923375</v>
+        <v>6923358</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622592</v>
+        <v>132622591</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604966</v>
+        <v>604963</v>
       </c>
       <c r="R52" t="n">
-        <v>6923358</v>
+        <v>6923375</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6792,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132622601</v>
+        <v>132622590</v>
       </c>
       <c r="B62" t="n">
-        <v>79365</v>
+        <v>5199</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>604915</v>
+        <v>604925</v>
       </c>
       <c r="R62" t="n">
-        <v>6923304</v>
+        <v>6923398</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6899,7 +6899,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622599</v>
+        <v>132622601</v>
       </c>
       <c r="B63" t="n">
         <v>79365</v>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604882</v>
+        <v>604915</v>
       </c>
       <c r="R63" t="n">
-        <v>6923308</v>
+        <v>6923304</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,32 +7006,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622590</v>
+        <v>132622599</v>
       </c>
       <c r="B64" t="n">
-        <v>5199</v>
+        <v>79365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604925</v>
+        <v>604882</v>
       </c>
       <c r="R64" t="n">
-        <v>6923398</v>
+        <v>6923308</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7113,10 +7113,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132622596</v>
+        <v>132623161</v>
       </c>
       <c r="B65" t="n">
-        <v>79365</v>
+        <v>58119</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7124,37 +7124,49 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>604888</v>
+        <v>604889</v>
       </c>
       <c r="R65" t="n">
-        <v>6923300</v>
+        <v>6923338</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7178,22 +7190,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7220,10 +7222,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132623161</v>
+        <v>132622596</v>
       </c>
       <c r="B66" t="n">
-        <v>58119</v>
+        <v>79365</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7231,49 +7233,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>604889</v>
+        <v>604888</v>
       </c>
       <c r="R66" t="n">
-        <v>6923338</v>
+        <v>6923300</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7297,12 +7287,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -6346,32 +6346,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132622589</v>
+        <v>132622598</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R58" t="n">
-        <v>6923397</v>
+        <v>6923306</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6426,12 +6426,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>130 ex</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6458,32 +6453,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132622598</v>
+        <v>132622589</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6493,10 +6488,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>604882</v>
+        <v>604906</v>
       </c>
       <c r="R59" t="n">
-        <v>6923306</v>
+        <v>6923397</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6528,7 +6523,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6538,7 +6533,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>130 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6792,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132622590</v>
+        <v>132622601</v>
       </c>
       <c r="B62" t="n">
-        <v>5199</v>
+        <v>79365</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>604925</v>
+        <v>604915</v>
       </c>
       <c r="R62" t="n">
-        <v>6923398</v>
+        <v>6923304</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6899,7 +6899,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622601</v>
+        <v>132622599</v>
       </c>
       <c r="B63" t="n">
         <v>79365</v>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604915</v>
+        <v>604882</v>
       </c>
       <c r="R63" t="n">
-        <v>6923304</v>
+        <v>6923308</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,32 +7006,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622599</v>
+        <v>132622590</v>
       </c>
       <c r="B64" t="n">
-        <v>79365</v>
+        <v>5199</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604882</v>
+        <v>604925</v>
       </c>
       <c r="R64" t="n">
-        <v>6923308</v>
+        <v>6923398</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7113,10 +7113,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132623161</v>
+        <v>132622596</v>
       </c>
       <c r="B65" t="n">
-        <v>58119</v>
+        <v>79365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7124,49 +7124,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>604889</v>
+        <v>604888</v>
       </c>
       <c r="R65" t="n">
-        <v>6923338</v>
+        <v>6923300</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7190,12 +7178,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7222,10 +7220,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132622596</v>
+        <v>132623161</v>
       </c>
       <c r="B66" t="n">
-        <v>79365</v>
+        <v>58119</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7233,37 +7231,49 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>604888</v>
+        <v>604889</v>
       </c>
       <c r="R66" t="n">
-        <v>6923300</v>
+        <v>6923338</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7287,22 +7297,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622592</v>
+        <v>132622591</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604966</v>
+        <v>604963</v>
       </c>
       <c r="R51" t="n">
-        <v>6923358</v>
+        <v>6923375</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622591</v>
+        <v>132622592</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604963</v>
+        <v>604966</v>
       </c>
       <c r="R52" t="n">
-        <v>6923375</v>
+        <v>6923358</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6792,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132622601</v>
+        <v>132622590</v>
       </c>
       <c r="B62" t="n">
-        <v>79365</v>
+        <v>5199</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>604915</v>
+        <v>604925</v>
       </c>
       <c r="R62" t="n">
-        <v>6923304</v>
+        <v>6923398</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6899,7 +6899,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622599</v>
+        <v>132622601</v>
       </c>
       <c r="B63" t="n">
         <v>79365</v>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604882</v>
+        <v>604915</v>
       </c>
       <c r="R63" t="n">
-        <v>6923308</v>
+        <v>6923304</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,32 +7006,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622590</v>
+        <v>132622599</v>
       </c>
       <c r="B64" t="n">
-        <v>5199</v>
+        <v>79365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604925</v>
+        <v>604882</v>
       </c>
       <c r="R64" t="n">
-        <v>6923398</v>
+        <v>6923308</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622591</v>
+        <v>132622592</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604963</v>
+        <v>604966</v>
       </c>
       <c r="R51" t="n">
-        <v>6923375</v>
+        <v>6923358</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622592</v>
+        <v>132622591</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604966</v>
+        <v>604963</v>
       </c>
       <c r="R52" t="n">
-        <v>6923358</v>
+        <v>6923375</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6792,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132622590</v>
+        <v>132622601</v>
       </c>
       <c r="B62" t="n">
-        <v>5199</v>
+        <v>79365</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>604925</v>
+        <v>604915</v>
       </c>
       <c r="R62" t="n">
-        <v>6923398</v>
+        <v>6923304</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6899,7 +6899,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622601</v>
+        <v>132622599</v>
       </c>
       <c r="B63" t="n">
         <v>79365</v>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604915</v>
+        <v>604882</v>
       </c>
       <c r="R63" t="n">
-        <v>6923304</v>
+        <v>6923308</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,32 +7006,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622599</v>
+        <v>132622590</v>
       </c>
       <c r="B64" t="n">
-        <v>79365</v>
+        <v>5199</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604882</v>
+        <v>604925</v>
       </c>
       <c r="R64" t="n">
-        <v>6923308</v>
+        <v>6923398</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126244910</v>
+        <v>132622594</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604865</v>
+        <v>604901</v>
       </c>
       <c r="R2" t="n">
-        <v>6923197</v>
+        <v>6923297</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126244779</v>
+        <v>132622595</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604898</v>
+        <v>604886</v>
       </c>
       <c r="R3" t="n">
-        <v>6923266</v>
+        <v>6923295</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,57 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244573</v>
+        <v>132622596</v>
       </c>
       <c r="B4" t="n">
-        <v>56852</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604843</v>
+        <v>604888</v>
       </c>
       <c r="R4" t="n">
-        <v>6923281</v>
+        <v>6923300</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,17 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En vuxen och en unge</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126243913</v>
+        <v>132622599</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604846</v>
+        <v>604882</v>
       </c>
       <c r="R5" t="n">
-        <v>6923320</v>
+        <v>6923308</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126244314</v>
+        <v>132622600</v>
       </c>
       <c r="B6" t="n">
-        <v>91699</v>
+        <v>79405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604829</v>
+        <v>604927</v>
       </c>
       <c r="R6" t="n">
-        <v>6923326</v>
+        <v>6923203</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126243134</v>
+        <v>132622601</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>79405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604973</v>
+        <v>604915</v>
       </c>
       <c r="R7" t="n">
-        <v>6923382</v>
+        <v>6923304</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1259,12 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126242980</v>
+        <v>126241171</v>
       </c>
       <c r="B8" t="n">
-        <v>91210</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604937</v>
+        <v>604931</v>
       </c>
       <c r="R8" t="n">
-        <v>6923369</v>
+        <v>6923243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126242691</v>
+        <v>126241533</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,39 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604953</v>
+        <v>604952</v>
       </c>
       <c r="R9" t="n">
-        <v>6923370</v>
+        <v>6923317</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126241081</v>
+        <v>126242636</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604931</v>
+        <v>604970</v>
       </c>
       <c r="R10" t="n">
-        <v>6923243</v>
+        <v>6923359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126244102</v>
+        <v>126243134</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1612,12 +1628,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604829</v>
+        <v>604973</v>
       </c>
       <c r="R11" t="n">
-        <v>6923326</v>
+        <v>6923382</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126244721</v>
+        <v>126243781</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,39 +1716,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604909</v>
+        <v>604846</v>
       </c>
       <c r="R12" t="n">
-        <v>6923259</v>
+        <v>6923320</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126244493</v>
+        <v>126244102</v>
       </c>
       <c r="B13" t="n">
-        <v>100543</v>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604804</v>
+        <v>604829</v>
       </c>
       <c r="R13" t="n">
-        <v>6923297</v>
+        <v>6923326</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126242541</v>
+        <v>129337878</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1904,39 +1910,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604966</v>
+        <v>604921</v>
       </c>
       <c r="R14" t="n">
-        <v>6923343</v>
+        <v>6923229</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,17 +1964,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126242864</v>
+        <v>129338152</v>
       </c>
       <c r="B15" t="n">
-        <v>97239</v>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604927</v>
+        <v>604818</v>
       </c>
       <c r="R15" t="n">
-        <v>6923374</v>
+        <v>6923289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,12 +2061,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2097,10 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126243475</v>
+        <v>129338296</v>
       </c>
       <c r="B16" t="n">
-        <v>91245</v>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2104,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604893</v>
+        <v>604836</v>
       </c>
       <c r="R16" t="n">
-        <v>6923384</v>
+        <v>6923306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,12 +2158,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2194,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126243781</v>
+        <v>129339518</v>
       </c>
       <c r="B17" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2214,12 +2210,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604846</v>
+        <v>604884</v>
       </c>
       <c r="R17" t="n">
-        <v>6923320</v>
+        <v>6923356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,12 +2255,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2291,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126241171</v>
+        <v>129339832</v>
       </c>
       <c r="B18" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,12 +2307,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604931</v>
+        <v>604906</v>
       </c>
       <c r="R18" t="n">
-        <v>6923243</v>
+        <v>6923435</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,12 +2352,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126242290</v>
+        <v>129339952</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,39 +2395,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>605003</v>
+        <v>604930</v>
       </c>
       <c r="R19" t="n">
-        <v>6923334</v>
+        <v>6923439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,17 +2449,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2495,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126241533</v>
+        <v>129340521</v>
       </c>
       <c r="B20" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2515,12 +2501,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2530,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604952</v>
+        <v>604965</v>
       </c>
       <c r="R20" t="n">
-        <v>6923317</v>
+        <v>6923388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,12 +2546,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2592,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126242587</v>
+        <v>126241081</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>604966</v>
+        <v>604931</v>
       </c>
       <c r="R21" t="n">
-        <v>6923343</v>
+        <v>6923243</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2675,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126242839</v>
+        <v>126241476</v>
       </c>
       <c r="B22" t="n">
-        <v>91699</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>604916</v>
+        <v>604946</v>
       </c>
       <c r="R22" t="n">
-        <v>6923365</v>
+        <v>6923307</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126241476</v>
+        <v>126242587</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>604946</v>
+        <v>604966</v>
       </c>
       <c r="R23" t="n">
-        <v>6923307</v>
+        <v>6923343</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,10 +2869,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126241499</v>
+        <v>126243475</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2894,43 +2880,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>604927</v>
+        <v>604893</v>
       </c>
       <c r="R24" t="n">
-        <v>6923303</v>
+        <v>6923384</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,54 +2966,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126244626</v>
+        <v>126243913</v>
       </c>
       <c r="B25" t="n">
-        <v>58027</v>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>604909</v>
+        <v>604846</v>
       </c>
       <c r="R25" t="n">
-        <v>6923259</v>
+        <v>6923320</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126242636</v>
+        <v>129339099</v>
       </c>
       <c r="B26" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3130,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>604970</v>
+        <v>604943</v>
       </c>
       <c r="R26" t="n">
-        <v>6923359</v>
+        <v>6923291</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,12 +3128,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3192,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126244096</v>
+        <v>129339193</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3203,42 +3171,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>604836</v>
+        <v>604952</v>
       </c>
       <c r="R27" t="n">
-        <v>6923306</v>
+        <v>6923317</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3265,17 +3225,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sannolikt bohål från tretåig hackspett. Bohålets innerdiameter är ca 4,5 cm och sitter omkring 2m ovan mark i en död gran.</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3302,10 +3257,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129339518</v>
+        <v>129339569</v>
       </c>
       <c r="B28" t="n">
-        <v>91891</v>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3313,21 +3268,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3337,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>604884</v>
+        <v>604895</v>
       </c>
       <c r="R28" t="n">
-        <v>6923356</v>
+        <v>6923362</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129339099</v>
+        <v>132622592</v>
       </c>
       <c r="B29" t="n">
-        <v>91593</v>
+        <v>91974</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,13 +3389,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>604943</v>
+        <v>604966</v>
       </c>
       <c r="R29" t="n">
-        <v>6923291</v>
+        <v>6923358</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3464,12 +3419,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3496,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129338296</v>
+        <v>126242839</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>92369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3507,21 +3472,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3531,10 +3496,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>604836</v>
+        <v>604916</v>
       </c>
       <c r="R30" t="n">
-        <v>6923306</v>
+        <v>6923365</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3561,12 +3526,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3593,32 +3558,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129340170</v>
+        <v>126244280</v>
       </c>
       <c r="B31" t="n">
-        <v>80090</v>
+        <v>92369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3628,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>604927</v>
+        <v>604829</v>
       </c>
       <c r="R31" t="n">
-        <v>6923404</v>
+        <v>6923326</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3658,12 +3623,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3690,49 +3655,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129340708</v>
+        <v>129338318</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>92369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>604970</v>
+        <v>604826</v>
       </c>
       <c r="R32" t="n">
-        <v>6923359</v>
+        <v>6923299</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,10 +3752,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129339952</v>
+        <v>129339480</v>
       </c>
       <c r="B33" t="n">
-        <v>91891</v>
+        <v>92369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3802,21 +3763,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3826,10 +3787,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>604930</v>
+        <v>604884</v>
       </c>
       <c r="R33" t="n">
-        <v>6923439</v>
+        <v>6923356</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3888,32 +3849,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129340521</v>
+        <v>126242980</v>
       </c>
       <c r="B34" t="n">
-        <v>91891</v>
+        <v>91872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3923,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>604965</v>
+        <v>604937</v>
       </c>
       <c r="R34" t="n">
-        <v>6923388</v>
+        <v>6923369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,12 +3914,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3985,32 +3946,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339193</v>
+        <v>132622591</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4020,13 +3981,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>604952</v>
+        <v>604963</v>
       </c>
       <c r="R35" t="n">
-        <v>6923317</v>
+        <v>6923375</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4050,12 +4011,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4082,32 +4053,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129339569</v>
+        <v>132622598</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4117,13 +4088,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>604895</v>
+        <v>604882</v>
       </c>
       <c r="R36" t="n">
-        <v>6923362</v>
+        <v>6923306</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4147,12 +4118,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4179,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129337878</v>
+        <v>132622587</v>
       </c>
       <c r="B37" t="n">
-        <v>91891</v>
+        <v>75468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4190,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4214,13 +4195,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>604921</v>
+        <v>604903</v>
       </c>
       <c r="R37" t="n">
-        <v>6923229</v>
+        <v>6923396</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4244,12 +4225,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4276,32 +4267,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129339480</v>
+        <v>129339612</v>
       </c>
       <c r="B38" t="n">
-        <v>92046</v>
+        <v>80336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4311,10 +4302,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>604884</v>
+        <v>604882</v>
       </c>
       <c r="R38" t="n">
-        <v>6923356</v>
+        <v>6923385</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,32 +4364,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129339832</v>
+        <v>129339682</v>
       </c>
       <c r="B39" t="n">
-        <v>91891</v>
+        <v>80336</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4408,10 +4399,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>604906</v>
+        <v>604882</v>
       </c>
       <c r="R39" t="n">
-        <v>6923435</v>
+        <v>6923394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129339682</v>
+        <v>129340170</v>
       </c>
       <c r="B40" t="n">
-        <v>80090</v>
+        <v>80336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4505,10 +4496,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>604882</v>
+        <v>604927</v>
       </c>
       <c r="R40" t="n">
-        <v>6923394</v>
+        <v>6923404</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,32 +4558,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129338318</v>
+        <v>132622586</v>
       </c>
       <c r="B41" t="n">
-        <v>92046</v>
+        <v>79629</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6459</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4602,13 +4593,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>604826</v>
+        <v>604933</v>
       </c>
       <c r="R41" t="n">
-        <v>6923299</v>
+        <v>6923265</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4632,12 +4623,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4664,37 +4665,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129341014</v>
+        <v>126242218</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4703,10 +4705,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>604934</v>
+        <v>605009</v>
       </c>
       <c r="R42" t="n">
-        <v>6923350</v>
+        <v>6923310</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4733,12 +4735,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4765,37 +4772,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129339379</v>
+        <v>126242262</v>
       </c>
       <c r="B43" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4804,10 +4812,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>604930</v>
+        <v>605003</v>
       </c>
       <c r="R43" t="n">
-        <v>6923339</v>
+        <v>6923334</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4834,12 +4842,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4866,10 +4879,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129338152</v>
+        <v>126242541</v>
       </c>
       <c r="B44" t="n">
-        <v>91891</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,34 +4890,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>604818</v>
+        <v>604966</v>
       </c>
       <c r="R44" t="n">
-        <v>6923289</v>
+        <v>6923343</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4931,12 +4949,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4963,45 +4986,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129339612</v>
+        <v>126242691</v>
       </c>
       <c r="B45" t="n">
-        <v>80090</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>604882</v>
+        <v>604953</v>
       </c>
       <c r="R45" t="n">
-        <v>6923385</v>
+        <v>6923370</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5028,12 +5056,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5060,49 +5093,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129339335</v>
+        <v>126244096</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>604921</v>
+        <v>604836</v>
       </c>
       <c r="R46" t="n">
-        <v>6923330</v>
+        <v>6923306</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5129,12 +5166,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sannolikt bohål från tretåig hackspett. Bohålets innerdiameter är ca 4,5 cm och sitter omkring 2m ovan mark i en död gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,37 +5203,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129339943</v>
+        <v>126244434</v>
       </c>
       <c r="B47" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5200,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>604922</v>
+        <v>604788</v>
       </c>
       <c r="R47" t="n">
-        <v>6923448</v>
+        <v>6923308</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5230,12 +5273,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5262,10 +5310,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129338835</v>
+        <v>126244721</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5293,7 +5341,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5302,10 +5350,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>604973</v>
+        <v>604909</v>
       </c>
       <c r="R48" t="n">
-        <v>6923267</v>
+        <v>6923259</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5332,17 +5380,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5369,10 +5417,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129339146</v>
+        <v>126244779</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5409,10 +5457,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>604952</v>
+        <v>604898</v>
       </c>
       <c r="R49" t="n">
-        <v>6923317</v>
+        <v>6923266</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5439,17 +5487,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5476,10 +5524,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129340964</v>
+        <v>126244910</v>
       </c>
       <c r="B50" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5516,10 +5564,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>604921</v>
+        <v>604865</v>
       </c>
       <c r="R50" t="n">
-        <v>6923330</v>
+        <v>6923197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5546,12 +5594,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -5583,10 +5631,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132622592</v>
+        <v>129338835</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,37 +5642,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>604966</v>
+        <v>604973</v>
       </c>
       <c r="R51" t="n">
-        <v>6923358</v>
+        <v>6923267</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5648,22 +5701,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>18:35</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>18:35</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5690,10 +5738,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132622591</v>
+        <v>129339146</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5701,37 +5749,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>604963</v>
+        <v>604952</v>
       </c>
       <c r="R52" t="n">
-        <v>6923375</v>
+        <v>6923317</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5755,22 +5808,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>18:32</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>18:32</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5797,48 +5845,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132622587</v>
+        <v>129340964</v>
       </c>
       <c r="B53" t="n">
-        <v>75433</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6426</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>604903</v>
+        <v>604921</v>
       </c>
       <c r="R53" t="n">
-        <v>6923396</v>
+        <v>6923330</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5862,22 +5915,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>18:18</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>18:18</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5904,10 +5952,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132622594</v>
+        <v>132622597</v>
       </c>
       <c r="B54" t="n">
-        <v>79365</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,34 +5963,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>604901</v>
+        <v>604883</v>
       </c>
       <c r="R54" t="n">
-        <v>6923297</v>
+        <v>6923304</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5974,7 +6030,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -5984,7 +6040,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6011,10 +6072,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132622600</v>
+        <v>132623034</v>
       </c>
       <c r="B55" t="n">
-        <v>79365</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,37 +6083,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>604927</v>
+        <v>604910</v>
       </c>
       <c r="R55" t="n">
-        <v>6923203</v>
+        <v>6923344</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6079,19 +6152,14 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>17:25</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Två tretåiga hackspettar som trummar till varandra.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6118,14 +6186,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132623165</v>
+        <v>132622593</v>
       </c>
       <c r="B56" t="n">
-        <v>57136</v>
+        <v>57153</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6161,17 +6229,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>604935</v>
+        <v>604969</v>
       </c>
       <c r="R56" t="n">
         <v>6923321</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6195,12 +6263,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,14 +6305,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132622593</v>
+        <v>132623165</v>
       </c>
       <c r="B57" t="n">
-        <v>57136</v>
+        <v>57153</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6270,17 +6348,17 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>604969</v>
+        <v>604935</v>
       </c>
       <c r="R57" t="n">
         <v>6923321</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6304,22 +6382,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6346,48 +6414,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132622598</v>
+        <v>126244573</v>
       </c>
       <c r="B58" t="n">
-        <v>79333</v>
+        <v>57144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>604882</v>
+        <v>604843</v>
       </c>
       <c r="R58" t="n">
-        <v>6923306</v>
+        <v>6923281</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6411,22 +6488,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>19:11</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>19:11</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>En vuxen och en unge</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6453,48 +6525,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132622589</v>
+        <v>126244626</v>
       </c>
       <c r="B59" t="n">
-        <v>99130</v>
+        <v>58327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>604906</v>
+        <v>604909</v>
       </c>
       <c r="R59" t="n">
-        <v>6923397</v>
+        <v>6923259</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6518,27 +6599,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>18:19</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>130 ex</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6565,48 +6631,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132622586</v>
+        <v>126241499</v>
       </c>
       <c r="B60" t="n">
-        <v>79589</v>
+        <v>58114</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6459</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>604933</v>
+        <v>604927</v>
       </c>
       <c r="R60" t="n">
-        <v>6923265</v>
+        <v>6923303</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6630,22 +6705,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>17:52</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>17:52</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6672,10 +6737,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132622597</v>
+        <v>132623161</v>
       </c>
       <c r="B61" t="n">
-        <v>57958</v>
+        <v>58136</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6683,45 +6748,49 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Mpd</t>
+          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>604883</v>
+        <v>604889</v>
       </c>
       <c r="R61" t="n">
-        <v>6923304</v>
+        <v>6923338</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6745,27 +6814,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>19:11</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6792,32 +6846,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132622601</v>
+        <v>132622590</v>
       </c>
       <c r="B62" t="n">
-        <v>79365</v>
+        <v>5201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6881,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>604915</v>
+        <v>604925</v>
       </c>
       <c r="R62" t="n">
-        <v>6923304</v>
+        <v>6923398</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6857,22 +6911,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6899,48 +6953,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132622599</v>
+        <v>129339335</v>
       </c>
       <c r="B63" t="n">
-        <v>79365</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>604882</v>
+        <v>604921</v>
       </c>
       <c r="R63" t="n">
-        <v>6923308</v>
+        <v>6923330</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,22 +7022,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>19:12</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>19:12</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,48 +7054,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132622590</v>
+        <v>129339379</v>
       </c>
       <c r="B64" t="n">
-        <v>5199</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>604925</v>
+        <v>604930</v>
       </c>
       <c r="R64" t="n">
-        <v>6923398</v>
+        <v>6923339</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7071,22 +7123,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>18:24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>18:24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7113,48 +7155,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132622596</v>
+        <v>129339943</v>
       </c>
       <c r="B65" t="n">
-        <v>79365</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>604888</v>
+        <v>604922</v>
       </c>
       <c r="R65" t="n">
-        <v>6923300</v>
+        <v>6923448</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7178,22 +7224,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>19:08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7220,60 +7256,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132623161</v>
+        <v>129340708</v>
       </c>
       <c r="B66" t="n">
-        <v>58119</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>105</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>604889</v>
+        <v>604970</v>
       </c>
       <c r="R66" t="n">
-        <v>6923338</v>
+        <v>6923359</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7297,12 +7325,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7329,48 +7357,52 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132622595</v>
+        <v>129341014</v>
       </c>
       <c r="B67" t="n">
-        <v>79365</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>604886</v>
+        <v>604934</v>
       </c>
       <c r="R67" t="n">
-        <v>6923295</v>
+        <v>6923350</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7394,22 +7426,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7436,60 +7458,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132623034</v>
+        <v>132622589</v>
       </c>
       <c r="B68" t="n">
-        <v>57958</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skarpåsbodarna, Fittjesjön, Selånger, Mpd</t>
+          <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>604910</v>
+        <v>604906</v>
       </c>
       <c r="R68" t="n">
-        <v>6923344</v>
+        <v>6923397</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7513,17 +7523,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Två tretåiga hackspettar som trummar till varandra.</t>
+          <t>130 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7547,6 +7567,200 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126242864</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>604927</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6923374</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126244493</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skarpåsbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>604804</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6923297</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51104-2025 artfynd.xlsx
+++ b/artfynd/A 51104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622594</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622595</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622596</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622599</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622601</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126241171</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126241533</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242636</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243134</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243781</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244102</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129337878</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129338152</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129338296</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339518</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339832</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339952</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2575,6 +2670,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129340521</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2672,6 +2772,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126241081</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126241476</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242587</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243475</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3060,6 +3180,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243913</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3157,6 +3282,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339099</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3254,6 +3384,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339193</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3351,6 +3486,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339569</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3458,6 +3598,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622592</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3555,6 +3700,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242839</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3652,6 +3802,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244280</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3749,6 +3904,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129338318</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3846,6 +4006,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339480</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3943,6 +4108,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242980</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4050,6 +4220,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622591</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4157,6 +4332,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622598</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4264,6 +4444,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622587</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4361,6 +4546,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339612</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4458,6 +4648,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339682</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4555,6 +4750,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129340170</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4662,6 +4862,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622586</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4769,6 +4974,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242218</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4876,6 +5086,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242262</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4983,6 +5198,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242541</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5090,6 +5310,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242691</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5200,6 +5425,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244096</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5307,6 +5537,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244434</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5414,6 +5649,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244721</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5521,6 +5761,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244779</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5628,6 +5873,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244910</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5735,6 +5985,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129338835</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5842,6 +6097,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339146</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5949,6 +6209,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129340964</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6069,6 +6334,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622597</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6183,6 +6453,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623034</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6302,6 +6577,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622593</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6411,6 +6691,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623165</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6522,6 +6807,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244573</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6628,6 +6918,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244626</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6734,6 +7029,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126241499</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6843,6 +7143,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623161</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6950,6 +7255,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622590</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7051,6 +7361,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339335</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7152,6 +7467,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339379</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7253,6 +7573,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339943</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7354,6 +7679,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129340708</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7455,6 +7785,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341014</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7567,6 +7902,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132622589</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7664,6 +8004,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242864</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7761,8 +8106,84 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244493</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>